--- a/artfynd/A 28867-2025 artfynd.xlsx
+++ b/artfynd/A 28867-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017361</v>
       </c>
       <c r="B2" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126016944</v>
       </c>
       <c r="B3" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126016940</v>
       </c>
       <c r="B4" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>126017366</v>
       </c>
       <c r="B5" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126016945</v>
+        <v>126016941</v>
       </c>
       <c r="B6" t="n">
-        <v>98332</v>
+        <v>98251</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>763962</v>
+        <v>764001</v>
       </c>
       <c r="R6" t="n">
-        <v>7323779</v>
+        <v>7323674</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126016941</v>
+        <v>126016945</v>
       </c>
       <c r="B7" t="n">
-        <v>98249</v>
+        <v>98334</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>764001</v>
+        <v>763962</v>
       </c>
       <c r="R7" t="n">
-        <v>7323674</v>
+        <v>7323779</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>126017364</v>
       </c>
       <c r="B8" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>126016943</v>
       </c>
       <c r="B9" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>126017365</v>
       </c>
       <c r="B10" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>126017363</v>
       </c>
       <c r="B11" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>126016942</v>
       </c>
       <c r="B12" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>126017362</v>
       </c>
       <c r="B13" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 28867-2025 artfynd.xlsx
+++ b/artfynd/A 28867-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017361</v>
       </c>
       <c r="B2" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126016944</v>
       </c>
       <c r="B3" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126016940</v>
       </c>
       <c r="B4" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>126017366</v>
       </c>
       <c r="B5" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126016941</v>
+        <v>126016945</v>
       </c>
       <c r="B6" t="n">
-        <v>98251</v>
+        <v>98338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>764001</v>
+        <v>763962</v>
       </c>
       <c r="R6" t="n">
-        <v>7323674</v>
+        <v>7323779</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126016945</v>
+        <v>126016941</v>
       </c>
       <c r="B7" t="n">
-        <v>98334</v>
+        <v>98255</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>763962</v>
+        <v>764001</v>
       </c>
       <c r="R7" t="n">
-        <v>7323779</v>
+        <v>7323674</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>126017364</v>
       </c>
       <c r="B8" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>126016943</v>
       </c>
       <c r="B9" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>126017365</v>
       </c>
       <c r="B10" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>126017363</v>
       </c>
       <c r="B11" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>126016942</v>
       </c>
       <c r="B12" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>126017362</v>
       </c>
       <c r="B13" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 28867-2025 artfynd.xlsx
+++ b/artfynd/A 28867-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017361</v>
       </c>
       <c r="B2" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126016944</v>
       </c>
       <c r="B3" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126016940</v>
       </c>
       <c r="B4" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>126017366</v>
       </c>
       <c r="B5" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126016945</v>
+        <v>126016941</v>
       </c>
       <c r="B6" t="n">
-        <v>98338</v>
+        <v>98256</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>763962</v>
+        <v>764001</v>
       </c>
       <c r="R6" t="n">
-        <v>7323779</v>
+        <v>7323674</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126016941</v>
+        <v>126016945</v>
       </c>
       <c r="B7" t="n">
-        <v>98255</v>
+        <v>98339</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>764001</v>
+        <v>763962</v>
       </c>
       <c r="R7" t="n">
-        <v>7323674</v>
+        <v>7323779</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>126017364</v>
       </c>
       <c r="B8" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>126016943</v>
       </c>
       <c r="B9" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>126017365</v>
       </c>
       <c r="B10" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>126017363</v>
       </c>
       <c r="B11" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>126016942</v>
       </c>
       <c r="B12" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>126017362</v>
       </c>
       <c r="B13" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 28867-2025 artfynd.xlsx
+++ b/artfynd/A 28867-2025 artfynd.xlsx
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126016941</v>
+        <v>126016945</v>
       </c>
       <c r="B6" t="n">
-        <v>98256</v>
+        <v>98339</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>764001</v>
+        <v>763962</v>
       </c>
       <c r="R6" t="n">
-        <v>7323674</v>
+        <v>7323779</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126016945</v>
+        <v>126016941</v>
       </c>
       <c r="B7" t="n">
-        <v>98339</v>
+        <v>98256</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>763962</v>
+        <v>764001</v>
       </c>
       <c r="R7" t="n">
-        <v>7323779</v>
+        <v>7323674</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 28867-2025 artfynd.xlsx
+++ b/artfynd/A 28867-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017361</v>
       </c>
       <c r="B2" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126016944</v>
       </c>
       <c r="B3" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126016940</v>
       </c>
       <c r="B4" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>126017366</v>
       </c>
       <c r="B5" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126016945</v>
+        <v>126016941</v>
       </c>
       <c r="B6" t="n">
-        <v>98339</v>
+        <v>98258</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>763962</v>
+        <v>764001</v>
       </c>
       <c r="R6" t="n">
-        <v>7323779</v>
+        <v>7323674</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126016941</v>
+        <v>126016945</v>
       </c>
       <c r="B7" t="n">
-        <v>98256</v>
+        <v>98341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>764001</v>
+        <v>763962</v>
       </c>
       <c r="R7" t="n">
-        <v>7323674</v>
+        <v>7323779</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>126017364</v>
       </c>
       <c r="B8" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>126016943</v>
       </c>
       <c r="B9" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>126017365</v>
       </c>
       <c r="B10" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>126017363</v>
       </c>
       <c r="B11" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>126016942</v>
       </c>
       <c r="B12" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>126017362</v>
       </c>
       <c r="B13" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 28867-2025 artfynd.xlsx
+++ b/artfynd/A 28867-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017361</v>
       </c>
       <c r="B2" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126016944</v>
       </c>
       <c r="B3" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126016940</v>
       </c>
       <c r="B4" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>126017366</v>
       </c>
       <c r="B5" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126016941</v>
+        <v>126016945</v>
       </c>
       <c r="B6" t="n">
-        <v>98258</v>
+        <v>98343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>764001</v>
+        <v>763962</v>
       </c>
       <c r="R6" t="n">
-        <v>7323674</v>
+        <v>7323779</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126016945</v>
+        <v>126016941</v>
       </c>
       <c r="B7" t="n">
-        <v>98341</v>
+        <v>98260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>763962</v>
+        <v>764001</v>
       </c>
       <c r="R7" t="n">
-        <v>7323779</v>
+        <v>7323674</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>126017364</v>
       </c>
       <c r="B8" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>126016943</v>
       </c>
       <c r="B9" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>126017365</v>
       </c>
       <c r="B10" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>126017363</v>
       </c>
       <c r="B11" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>126016942</v>
       </c>
       <c r="B12" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>126017362</v>
       </c>
       <c r="B13" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 28867-2025 artfynd.xlsx
+++ b/artfynd/A 28867-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017361</v>
       </c>
       <c r="B2" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126016944</v>
       </c>
       <c r="B3" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126016940</v>
       </c>
       <c r="B4" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>126017366</v>
       </c>
       <c r="B5" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126016945</v>
+        <v>126016941</v>
       </c>
       <c r="B6" t="n">
-        <v>98343</v>
+        <v>98262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>763962</v>
+        <v>764001</v>
       </c>
       <c r="R6" t="n">
-        <v>7323779</v>
+        <v>7323674</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126016941</v>
+        <v>126016945</v>
       </c>
       <c r="B7" t="n">
-        <v>98260</v>
+        <v>98345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>764001</v>
+        <v>763962</v>
       </c>
       <c r="R7" t="n">
-        <v>7323674</v>
+        <v>7323779</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>126017364</v>
       </c>
       <c r="B8" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>126016943</v>
       </c>
       <c r="B9" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>126017365</v>
       </c>
       <c r="B10" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>126017363</v>
       </c>
       <c r="B11" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>126016942</v>
       </c>
       <c r="B12" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>126017362</v>
       </c>
       <c r="B13" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 28867-2025 artfynd.xlsx
+++ b/artfynd/A 28867-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017361</v>
       </c>
       <c r="B2" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126016944</v>
       </c>
       <c r="B3" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126016940</v>
       </c>
       <c r="B4" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>126017366</v>
       </c>
       <c r="B5" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>126016941</v>
       </c>
       <c r="B6" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>126016945</v>
       </c>
       <c r="B7" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>126017364</v>
       </c>
       <c r="B8" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>126016943</v>
       </c>
       <c r="B9" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>126017365</v>
       </c>
       <c r="B10" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>126017363</v>
       </c>
       <c r="B11" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>126016942</v>
       </c>
       <c r="B12" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>126017362</v>
       </c>
       <c r="B13" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 28867-2025 artfynd.xlsx
+++ b/artfynd/A 28867-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017361</v>
       </c>
       <c r="B2" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126016944</v>
       </c>
       <c r="B3" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126016940</v>
       </c>
       <c r="B4" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>126017366</v>
       </c>
       <c r="B5" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>126016941</v>
       </c>
       <c r="B6" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>126016945</v>
       </c>
       <c r="B7" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>126017364</v>
       </c>
       <c r="B8" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>126016943</v>
       </c>
       <c r="B9" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>126017365</v>
       </c>
       <c r="B10" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>126017363</v>
       </c>
       <c r="B11" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>126016942</v>
       </c>
       <c r="B12" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>126017362</v>
       </c>
       <c r="B13" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 28867-2025 artfynd.xlsx
+++ b/artfynd/A 28867-2025 artfynd.xlsx
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126016941</v>
+        <v>126016945</v>
       </c>
       <c r="B6" t="n">
-        <v>98269</v>
+        <v>98352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>764001</v>
+        <v>763962</v>
       </c>
       <c r="R6" t="n">
-        <v>7323674</v>
+        <v>7323779</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126016945</v>
+        <v>126016941</v>
       </c>
       <c r="B7" t="n">
-        <v>98352</v>
+        <v>98269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>763962</v>
+        <v>764001</v>
       </c>
       <c r="R7" t="n">
-        <v>7323779</v>
+        <v>7323674</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 28867-2025 artfynd.xlsx
+++ b/artfynd/A 28867-2025 artfynd.xlsx
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126016945</v>
+        <v>126016941</v>
       </c>
       <c r="B6" t="n">
-        <v>98352</v>
+        <v>98269</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>763962</v>
+        <v>764001</v>
       </c>
       <c r="R6" t="n">
-        <v>7323779</v>
+        <v>7323674</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126016941</v>
+        <v>126016945</v>
       </c>
       <c r="B7" t="n">
-        <v>98269</v>
+        <v>98352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>764001</v>
+        <v>763962</v>
       </c>
       <c r="R7" t="n">
-        <v>7323674</v>
+        <v>7323779</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 28867-2025 artfynd.xlsx
+++ b/artfynd/A 28867-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017361</v>
       </c>
       <c r="B2" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126016944</v>
       </c>
       <c r="B3" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126016940</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>126017366</v>
       </c>
       <c r="B5" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>126016945</v>
       </c>
       <c r="B6" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>126016941</v>
       </c>
       <c r="B7" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>126017364</v>
       </c>
       <c r="B8" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>126016943</v>
       </c>
       <c r="B9" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>126017365</v>
       </c>
       <c r="B10" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>126017363</v>
       </c>
       <c r="B11" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>126016942</v>
       </c>
       <c r="B12" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>126017362</v>
       </c>
       <c r="B13" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 28867-2025 artfynd.xlsx
+++ b/artfynd/A 28867-2025 artfynd.xlsx
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126016945</v>
+        <v>126016941</v>
       </c>
       <c r="B6" t="n">
-        <v>98361</v>
+        <v>98278</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>763962</v>
+        <v>764001</v>
       </c>
       <c r="R6" t="n">
-        <v>7323779</v>
+        <v>7323674</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126016941</v>
+        <v>126016945</v>
       </c>
       <c r="B7" t="n">
-        <v>98278</v>
+        <v>98361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>764001</v>
+        <v>763962</v>
       </c>
       <c r="R7" t="n">
-        <v>7323674</v>
+        <v>7323779</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 28867-2025 artfynd.xlsx
+++ b/artfynd/A 28867-2025 artfynd.xlsx
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126016941</v>
+        <v>126016945</v>
       </c>
       <c r="B6" t="n">
-        <v>98278</v>
+        <v>98361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>764001</v>
+        <v>763962</v>
       </c>
       <c r="R6" t="n">
-        <v>7323674</v>
+        <v>7323779</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126016945</v>
+        <v>126016941</v>
       </c>
       <c r="B7" t="n">
-        <v>98361</v>
+        <v>98278</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>763962</v>
+        <v>764001</v>
       </c>
       <c r="R7" t="n">
-        <v>7323779</v>
+        <v>7323674</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 28867-2025 artfynd.xlsx
+++ b/artfynd/A 28867-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126017361</v>
+        <v>126016940</v>
       </c>
       <c r="B2" t="n">
-        <v>98361</v>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>763961</v>
+        <v>764013</v>
       </c>
       <c r="R2" t="n">
-        <v>7323779</v>
+        <v>7323671</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -744,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126016944</v>
+        <v>126016941</v>
       </c>
       <c r="B3" t="n">
-        <v>98278</v>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,13 +820,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>763966</v>
+        <v>764001</v>
       </c>
       <c r="R3" t="n">
-        <v>7323731</v>
+        <v>7323674</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126016940</v>
+        <v>126016942</v>
       </c>
       <c r="B4" t="n">
-        <v>98278</v>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,13 +926,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>764013</v>
+        <v>763991</v>
       </c>
       <c r="R4" t="n">
-        <v>7323671</v>
+        <v>7323683</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126017366</v>
+        <v>126016943</v>
       </c>
       <c r="B5" t="n">
-        <v>98278</v>
+        <v>99035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,13 +1032,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>763960</v>
+        <v>763977</v>
       </c>
       <c r="R5" t="n">
-        <v>7323716</v>
+        <v>7323707</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126016941</v>
+        <v>126016944</v>
       </c>
       <c r="B6" t="n">
-        <v>98278</v>
+        <v>99035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>764001</v>
+        <v>763966</v>
       </c>
       <c r="R6" t="n">
-        <v>7323674</v>
+        <v>7323731</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126016945</v>
+        <v>126017362</v>
       </c>
       <c r="B7" t="n">
-        <v>98361</v>
+        <v>99035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>763962</v>
+        <v>763961</v>
       </c>
       <c r="R7" t="n">
-        <v>7323779</v>
+        <v>7323732</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126017364</v>
+        <v>126017363</v>
       </c>
       <c r="B8" t="n">
-        <v>98278</v>
+        <v>99035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>763983</v>
+        <v>763987</v>
       </c>
       <c r="R8" t="n">
-        <v>7323687</v>
+        <v>7323685</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126016943</v>
+        <v>126017364</v>
       </c>
       <c r="B9" t="n">
-        <v>98278</v>
+        <v>99035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,13 +1456,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>763977</v>
+        <v>763983</v>
       </c>
       <c r="R9" t="n">
-        <v>7323707</v>
+        <v>7323687</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1526,7 +1526,7 @@
         <v>126017365</v>
       </c>
       <c r="B10" t="n">
-        <v>98278</v>
+        <v>99035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126017363</v>
+        <v>126017366</v>
       </c>
       <c r="B11" t="n">
-        <v>98278</v>
+        <v>99035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>763987</v>
+        <v>763960</v>
       </c>
       <c r="R11" t="n">
-        <v>7323685</v>
+        <v>7323716</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1735,32 +1735,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126016942</v>
+        <v>126016945</v>
       </c>
       <c r="B12" t="n">
-        <v>98278</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1774,10 +1774,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>763991</v>
+        <v>763962</v>
       </c>
       <c r="R12" t="n">
-        <v>7323683</v>
+        <v>7323779</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,32 +1841,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126017362</v>
+        <v>126017361</v>
       </c>
       <c r="B13" t="n">
-        <v>98278</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1883,7 +1883,7 @@
         <v>763961</v>
       </c>
       <c r="R13" t="n">
-        <v>7323732</v>
+        <v>7323779</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1910,12 +1910,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">

--- a/artfynd/A 28867-2025 artfynd.xlsx
+++ b/artfynd/A 28867-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126016940</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126016941</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126016942</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126016943</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126016944</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017362</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017363</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017364</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017365</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017366</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1838,6 +1893,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126016945</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1944,8 +2004,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017361</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>